--- a/event_planner_forms/001_thanksgiving_potluck_survey--event_planner_forms.xlsx
+++ b/event_planner_forms/001_thanksgiving_potluck_survey--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,8 +888,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -917,12 +917,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'turkey',_'value':_'turkey'}</t>
+          <t>turkey</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Turkey', 'value': 'turkey'}</t>
+          <t>Turkey</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'ham',_'value':_'ham'}</t>
+          <t>ham</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Ham', 'value': 'ham'}</t>
+          <t>Ham</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'veggie',_'value':_'veggie'}</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Veggie', 'value': 'veggie'}</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'mashed_potatoes',_'value':_'mashed_potatoes'}</t>
+          <t>mashed_potatoes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Mashed Potatoes', 'value': 'mashed_potatoes'}</t>
+          <t>Mashed Potatoes</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'green_bean_casserole',_'value':_'green_bean_casserole'}</t>
+          <t>green_bean_casserole</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Green Bean Casserole', 'value': 'green_bean_casserole'}</t>
+          <t>Green Bean Casserole</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'pumpkin_pie',_'value':_'pumpkin_pie'}</t>
+          <t>pumpkin_pie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Pumpkin Pie', 'value': 'pumpkin_pie'}</t>
+          <t>Pumpkin Pie</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'apple_pie',_'value':_'apple_pie'}</t>
+          <t>apple_pie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Apple Pie', 'value': 'apple_pie'}</t>
+          <t>Apple Pie</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
